--- a/docs/demo-data/GNDEC/GNDEC_4_ME.xlsx
+++ b/docs/demo-data/GNDEC/GNDEC_4_ME.xlsx
@@ -874,7 +874,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Er. Harleen Randhawa</t>
+          <t>Prof. Harleen Randhawa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -919,7 +919,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Er. Amandeep Mittal</t>
+          <t>Dr. Amandeep Mittal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -934,7 +934,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dr. Parminder Cheema</t>
+          <t>Prof. Parminder Cheema</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -949,7 +949,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Prof. Simranjit Mann</t>
+          <t>Dr. Simranjit Mann</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -964,7 +964,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Er. Kulwinder Khanna</t>
+          <t>Prof. Kulwinder Khanna</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1009,7 +1009,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Er. Jagmeet Toor</t>
+          <t>Dr. Jagmeet Toor</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1024,7 +1024,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dr. Tejinder Bedi</t>
+          <t>Prof. Tejinder Bedi</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1039,7 +1039,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Prof. Manveer Anand</t>
+          <t>Dr. Manveer Anand</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1054,7 +1054,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Er. Inderpreet Garg</t>
+          <t>Prof. Inderpreet Garg</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1482,7 +1482,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Er. Harleen Randhawa</t>
+          <t>Prof. Harleen Randhawa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1527,7 +1527,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Er. Amandeep Mittal</t>
+          <t>Dr. Amandeep Mittal</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1542,7 +1542,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dr. Parminder Cheema</t>
+          <t>Prof. Parminder Cheema</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1557,7 +1557,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Prof. Simranjit Mann</t>
+          <t>Dr. Simranjit Mann</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1572,7 +1572,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Er. Kulwinder Khanna</t>
+          <t>Prof. Kulwinder Khanna</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Er. Jagmeet Toor</t>
+          <t>Dr. Jagmeet Toor</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1632,7 +1632,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dr. Tejinder Bedi</t>
+          <t>Prof. Tejinder Bedi</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1647,7 +1647,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Prof. Manveer Anand</t>
+          <t>Dr. Manveer Anand</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1662,7 +1662,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Er. Inderpreet Garg</t>
+          <t>Prof. Inderpreet Garg</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Er. Harleen Randhawa</t>
+          <t>Prof. Harleen Randhawa</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1737,7 +1737,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Er. Harleen Randhawa</t>
+          <t>Prof. Harleen Randhawa</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1767,7 +1767,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Er. Harleen Randhawa</t>
+          <t>Prof. Harleen Randhawa</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1797,7 +1797,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Prof. Simranjit Mann</t>
+          <t>Dr. Simranjit Mann</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1812,7 +1812,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Er. Kulwinder Khanna</t>
+          <t>Prof. Kulwinder Khanna</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1827,7 +1827,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dr. Parminder Cheema</t>
+          <t>Prof. Parminder Cheema</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1842,7 +1842,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Er. Kulwinder Khanna</t>
+          <t>Prof. Kulwinder Khanna</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1857,7 +1857,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dr. Parminder Cheema</t>
+          <t>Prof. Parminder Cheema</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1872,7 +1872,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Prof. Simranjit Mann</t>
+          <t>Dr. Simranjit Mann</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1887,7 +1887,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Dr. Parminder Cheema</t>
+          <t>Prof. Parminder Cheema</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1902,7 +1902,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Prof. Simranjit Mann</t>
+          <t>Dr. Simranjit Mann</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dr. Parminder Cheema</t>
+          <t>Prof. Parminder Cheema</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1932,7 +1932,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Prof. Simranjit Mann</t>
+          <t>Dr. Simranjit Mann</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1947,7 +1947,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Dr. Tejinder Bedi</t>
+          <t>Prof. Tejinder Bedi</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1962,7 +1962,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Prof. Manveer Anand</t>
+          <t>Dr. Manveer Anand</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1977,7 +1977,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Er. Jagmeet Toor</t>
+          <t>Dr. Jagmeet Toor</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1992,7 +1992,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Prof. Manveer Anand</t>
+          <t>Dr. Manveer Anand</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2007,7 +2007,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Er. Jagmeet Toor</t>
+          <t>Dr. Jagmeet Toor</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2022,7 +2022,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Dr. Tejinder Bedi</t>
+          <t>Prof. Tejinder Bedi</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2037,7 +2037,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Er. Jagmeet Toor</t>
+          <t>Dr. Jagmeet Toor</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2052,7 +2052,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Dr. Tejinder Bedi</t>
+          <t>Prof. Tejinder Bedi</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Prof. Rupinder Jindal</t>
+          <t>Dr. Rupinder Jindal</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Prof. Rupinder Jindal</t>
+          <t>Dr. Rupinder Jindal</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Prof. Rupinder Jindal</t>
+          <t>Dr. Rupinder Jindal</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Prof. Tejinder Mann</t>
+          <t>Dr. Tejinder Mann</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dr. Pooja Bansal</t>
+          <t>Prof. Pooja Bansal</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dr. Pooja Bansal</t>
+          <t>Prof. Pooja Bansal</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Er. Aman Bains</t>
+          <t>Dr. Aman Bains</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Er. Harleen Randhawa</t>
+          <t>Prof. Harleen Randhawa</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Er. Harleen Randhawa</t>
+          <t>Prof. Harleen Randhawa</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Er. Harleen Randhawa</t>
+          <t>Prof. Harleen Randhawa</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Er. Harleen Randhawa</t>
+          <t>Prof. Harleen Randhawa</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Er. Harleen Randhawa</t>
+          <t>Prof. Harleen Randhawa</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Er. Harleen Randhawa</t>
+          <t>Prof. Harleen Randhawa</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Er. Amandeep Mittal</t>
+          <t>Dr. Amandeep Mittal</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Er. Amandeep Mittal</t>
+          <t>Dr. Amandeep Mittal</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Er. Amandeep Mittal</t>
+          <t>Dr. Amandeep Mittal</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Er. Amandeep Mittal</t>
+          <t>Dr. Amandeep Mittal</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Er. Amandeep Mittal</t>
+          <t>Dr. Amandeep Mittal</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Er. Amandeep Mittal</t>
+          <t>Dr. Amandeep Mittal</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dr. Parminder Cheema</t>
+          <t>Prof. Parminder Cheema</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dr. Parminder Cheema</t>
+          <t>Prof. Parminder Cheema</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dr. Parminder Cheema</t>
+          <t>Prof. Parminder Cheema</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Prof. Simranjit Mann</t>
+          <t>Dr. Simranjit Mann</t>
         </is>
       </c>
     </row>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Prof. Simranjit Mann</t>
+          <t>Dr. Simranjit Mann</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Prof. Simranjit Mann</t>
+          <t>Dr. Simranjit Mann</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Er. Kulwinder Khanna</t>
+          <t>Prof. Kulwinder Khanna</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Er. Jagmeet Toor</t>
+          <t>Dr. Jagmeet Toor</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Er. Jagmeet Toor</t>
+          <t>Dr. Jagmeet Toor</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Er. Jagmeet Toor</t>
+          <t>Dr. Jagmeet Toor</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dr. Tejinder Bedi</t>
+          <t>Prof. Tejinder Bedi</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dr. Tejinder Bedi</t>
+          <t>Prof. Tejinder Bedi</t>
         </is>
       </c>
     </row>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dr. Tejinder Bedi</t>
+          <t>Prof. Tejinder Bedi</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Prof. Manveer Anand</t>
+          <t>Dr. Manveer Anand</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Er. Inderpreet Garg</t>
+          <t>Prof. Inderpreet Garg</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Er. Inderpreet Garg</t>
+          <t>Prof. Inderpreet Garg</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabir Kaur</t>
+          <t>Mehakpreet Aulakh</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priya Mehta</t>
+          <t>Gurnoor Kaur</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Uday Dhillon</t>
+          <t>Rajbir Chawla</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rohan Kapoor</t>
+          <t>Harleen Gill</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sehaj Saini</t>
+          <t>Navjot Sidhu</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Japneet Jain</t>
+          <t>Sanya Malhi</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vihaan Bhatia</t>
+          <t>Gurleen Sandhu</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jasleen Sharma</t>
+          <t>Jashan Goyal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pranav Singh</t>
+          <t>Fatehbir Arora</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tanvi Arora</t>
+          <t>Prabhleen Aulakh</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Muskan Sandhu</t>
+          <t>Diya Kaur</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Noor Sidhu</t>
+          <t>Meher Chawla</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hargun Chawla</t>
+          <t>Sahil Gill</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sukhmani Aulakh</t>
+          <t>Aditi Sidhu</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ishaan Rana</t>
+          <t>Ekamjot Malhi</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nikita Pannu</t>
+          <t>Avneet Sandhu</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Simran Verma</t>
+          <t>Manjot Goyal</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Karan Gupta</t>
+          <t>Arjun Arora</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mehakpreet Bansal</t>
+          <t>Manav Thind</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gurnoor Grewal</t>
+          <t>Riya Singh</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rajbir Bedi</t>
+          <t>Zoya Bedi</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Harleen Thind</t>
+          <t>Arshdeep Sharma</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Navjot Goyal</t>
+          <t>Yuvraj Grewal</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sanya Malhi</t>
+          <t>Lovepreet Bhatia</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Gurleen Gill</t>
+          <t>Ananya Bansal</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jashan Kaur</t>
+          <t>Kavya Jain</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fatehbir Mehta</t>
+          <t>Rahul Gupta</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Prabhleen Dhillon</t>
+          <t>Vansh Saini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Diya Kapoor</t>
+          <t>Sneha Verma</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Meher Saini</t>
+          <t>Taranpreet Kapoor</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sahil Jain</t>
+          <t>Khushi Pannu</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Aditi Bhatia</t>
+          <t>Aarav Dhillon</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ekamjot Sharma</t>
+          <t>Kabir Rana</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Avneet Singh</t>
+          <t>Priya Mehta</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Manjot Arora</t>
+          <t>Vansh Jain</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Arjun Sandhu</t>
+          <t>Sneha Gupta</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Manav Sidhu</t>
+          <t>Taranpreet Saini</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Riya Chawla</t>
+          <t>Khushi Verma</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Zoya Aulakh</t>
+          <t>Aarav Kapoor</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Arshdeep Rana</t>
+          <t>Kabir Pannu</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Yuvraj Pannu</t>
+          <t>Priya Dhillon</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lovepreet Verma</t>
+          <t>Uday Rana</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ananya Gupta</t>
+          <t>Rohan Mehta</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Kavya Bansal</t>
+          <t>Sehaj Aulakh</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Rahul Grewal</t>
+          <t>Japneet Kaur</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Vansh Bedi</t>
+          <t>Vihaan Chawla</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sneha Thind</t>
+          <t>Jasleen Gill</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Taranpreet Goyal</t>
+          <t>Pranav Sidhu</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Khushi Malhi</t>
+          <t>Tanvi Malhi</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Aarav Gill</t>
+          <t>Muskan Sandhu</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Kabir Kaur</t>
+          <t>Noor Goyal</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Priya Mehta</t>
+          <t>Hargun Arora</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Uday Dhillon</t>
+          <t>Sukhmani Thind</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rohan Kapoor</t>
+          <t>Ishaan Singh</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sehaj Saini</t>
+          <t>Nikita Bedi</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Japneet Jain</t>
+          <t>Simran Sharma</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Vihaan Bhatia</t>
+          <t>Karan Grewal</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jasleen Sharma</t>
+          <t>Mehakpreet Bhatia</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pranav Singh</t>
+          <t>Gurnoor Bansal</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tanvi Arora</t>
+          <t>Rajbir Goyal</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Kabir Gupta</t>
+          <t>Harleen Arora</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Priya Bansal</t>
+          <t>Navjot Thind</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Uday Grewal</t>
+          <t>Sanya Singh</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Rohan Bedi</t>
+          <t>Gurleen Bedi</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sehaj Thind</t>
+          <t>Jashan Sharma</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Japneet Goyal</t>
+          <t>Fatehbir Grewal</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Vihaan Malhi</t>
+          <t>Prabhleen Bhatia</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Jasleen Gill</t>
+          <t>Diya Bansal</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Pranav Kaur</t>
+          <t>Meher Jain</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tanvi Mehta</t>
+          <t>Sahil Gupta</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Muskan Dhillon</t>
+          <t>Aditi Saini</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Noor Kapoor</t>
+          <t>Ekamjot Verma</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hargun Saini</t>
+          <t>Avneet Kapoor</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sukhmani Jain</t>
+          <t>Manjot Pannu</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ishaan Bhatia</t>
+          <t>Arjun Dhillon</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Nikita Sharma</t>
+          <t>Manav Rana</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Simran Singh</t>
+          <t>Riya Mehta</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Karan Arora</t>
+          <t>Zoya Aulakh</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mehakpreet Sandhu</t>
+          <t>Arshdeep Kaur</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Gurnoor Sidhu</t>
+          <t>Yuvraj Chawla</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Rajbir Chawla</t>
+          <t>Lovepreet Gill</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Harleen Aulakh</t>
+          <t>Ananya Sidhu</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Navjot Rana</t>
+          <t>Kavya Malhi</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sanya Pannu</t>
+          <t>Rahul Sandhu</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Gurleen Verma</t>
+          <t>Zoya Rana</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Jashan Gupta</t>
+          <t>Arshdeep Mehta</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Fatehbir Bansal</t>
+          <t>Yuvraj Aulakh</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Prabhleen Grewal</t>
+          <t>Lovepreet Kaur</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Diya Bedi</t>
+          <t>Ananya Chawla</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Meher Thind</t>
+          <t>Kavya Gill</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sahil Goyal</t>
+          <t>Rahul Sidhu</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Aditi Malhi</t>
+          <t>Vansh Malhi</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ekamjot Gill</t>
+          <t>Sneha Sandhu</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Avneet Kaur</t>
+          <t>Taranpreet Goyal</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Manjot Mehta</t>
+          <t>Khushi Arora</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Arjun Dhillon</t>
+          <t>Aarav Thind</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Manav Kapoor</t>
+          <t>Kabir Singh</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Riya Saini</t>
+          <t>Priya Bedi</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Zoya Jain</t>
+          <t>Uday Sharma</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Arshdeep Bhatia</t>
+          <t>Rohan Grewal</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Yuvraj Sharma</t>
+          <t>Sehaj Bhatia</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Lovepreet Singh</t>
+          <t>Japneet Bansal</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ananya Arora</t>
+          <t>Vihaan Jain</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Kavya Sandhu</t>
+          <t>Jasleen Gupta</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Rahul Sidhu</t>
+          <t>Pranav Saini</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Vansh Chawla</t>
+          <t>Tanvi Verma</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Sneha Aulakh</t>
+          <t>Muskan Kapoor</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6520,7 +6520,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Taranpreet Rana</t>
+          <t>Noor Pannu</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Khushi Pannu</t>
+          <t>Hargun Dhillon</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Aarav Verma</t>
+          <t>Sukhmani Bhatia</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Kabir Gupta</t>
+          <t>Ishaan Bansal</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Priya Bansal</t>
+          <t>Nikita Jain</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Uday Grewal</t>
+          <t>Simran Gupta</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Rohan Bedi</t>
+          <t>Karan Saini</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Sehaj Thind</t>
+          <t>Mehakpreet Verma</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Japneet Goyal</t>
+          <t>Gurnoor Kapoor</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Vihaan Malhi</t>
+          <t>Rajbir Pannu</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Jasleen Gill</t>
+          <t>Harleen Dhillon</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Pranav Kaur</t>
+          <t>Navjot Rana</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Tanvi Mehta</t>
+          <t>Sanya Mehta</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Muskan Dhillon</t>
+          <t>Gurleen Aulakh</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Noor Kapoor</t>
+          <t>Jashan Kaur</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Hargun Saini</t>
+          <t>Fatehbir Chawla</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Sukhmani Jain</t>
+          <t>Prabhleen Gill</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ishaan Bhatia</t>
+          <t>Diya Sidhu</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Nikita Sharma</t>
+          <t>Meher Malhi</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Simran Singh</t>
+          <t>Sahil Sandhu</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Karan Arora</t>
+          <t>Aditi Goyal</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Mehakpreet Sandhu</t>
+          <t>Ekamjot Arora</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Gurnoor Sidhu</t>
+          <t>Avneet Thind</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Rajbir Chawla</t>
+          <t>Manjot Singh</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Harleen Aulakh</t>
+          <t>Arjun Bedi</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Navjot Rana</t>
+          <t>Manav Sharma</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -7222,7 +7222,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Sanya Pannu</t>
+          <t>Riya Grewal</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -7249,7 +7249,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Gurleen Verma</t>
+          <t>Aditi Malhi</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Jashan Gupta</t>
+          <t>Ekamjot Sandhu</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Fatehbir Bansal</t>
+          <t>Avneet Goyal</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Prabhleen Grewal</t>
+          <t>Manjot Arora</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Diya Bedi</t>
+          <t>Arjun Thind</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Meher Thind</t>
+          <t>Manav Singh</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Sahil Goyal</t>
+          <t>Riya Bedi</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Aditi Malhi</t>
+          <t>Zoya Sharma</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ekamjot Gill</t>
+          <t>Arshdeep Grewal</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Avneet Kaur</t>
+          <t>Yuvraj Bhatia</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Manjot Mehta</t>
+          <t>Lovepreet Bansal</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Arjun Dhillon</t>
+          <t>Ananya Jain</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Manav Kapoor</t>
+          <t>Kavya Gupta</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Riya Saini</t>
+          <t>Rahul Saini</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -7627,7 +7627,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Zoya Jain</t>
+          <t>Vansh Verma</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Arshdeep Bhatia</t>
+          <t>Sneha Kapoor</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Yuvraj Sharma</t>
+          <t>Taranpreet Pannu</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Lovepreet Singh</t>
+          <t>Khushi Dhillon</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Ananya Arora</t>
+          <t>Aarav Rana</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Kavya Sandhu</t>
+          <t>Kabir Mehta</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Rahul Sidhu</t>
+          <t>Priya Aulakh</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Vansh Chawla</t>
+          <t>Uday Kaur</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Sneha Aulakh</t>
+          <t>Rohan Chawla</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Taranpreet Rana</t>
+          <t>Sehaj Gill</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Khushi Pannu</t>
+          <t>Japneet Sidhu</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Aarav Verma</t>
+          <t>Vihaan Pannu</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Kabir Gupta</t>
+          <t>Jasleen Dhillon</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Priya Bansal</t>
+          <t>Pranav Rana</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Uday Grewal</t>
+          <t>Tanvi Mehta</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Rohan Bedi</t>
+          <t>Muskan Aulakh</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Sehaj Thind</t>
+          <t>Noor Kaur</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Japneet Goyal</t>
+          <t>Hargun Chawla</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Vihaan Malhi</t>
+          <t>Sukhmani Gill</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Jasleen Gill</t>
+          <t>Ishaan Sidhu</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Pranav Kaur</t>
+          <t>Nikita Malhi</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Tanvi Mehta</t>
+          <t>Simran Sandhu</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Muskan Dhillon</t>
+          <t>Karan Goyal</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Noor Kapoor</t>
+          <t>Mehakpreet Arora</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Hargun Saini</t>
+          <t>Gurnoor Thind</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Sukhmani Jain</t>
+          <t>Rajbir Singh</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Ishaan Bhatia</t>
+          <t>Harleen Bedi</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Nikita Sharma</t>
+          <t>Navjot Sharma</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Simran Singh</t>
+          <t>Sanya Grewal</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Karan Arora</t>
+          <t>Gurleen Bhatia</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Kabir Arora</t>
+          <t>Jashan Bansal</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Priya Sandhu</t>
+          <t>Fatehbir Jain</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Uday Sidhu</t>
+          <t>Prabhleen Gupta</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Rohan Chawla</t>
+          <t>Diya Saini</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Sehaj Aulakh</t>
+          <t>Meher Verma</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Japneet Rana</t>
+          <t>Sahil Kapoor</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Vihaan Pannu</t>
+          <t>Gurleen Sharma</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Jasleen Verma</t>
+          <t>Jashan Grewal</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Pranav Gupta</t>
+          <t>Fatehbir Bhatia</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Tanvi Bansal</t>
+          <t>Prabhleen Bansal</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Muskan Grewal</t>
+          <t>Diya Jain</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -8734,7 +8734,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Noor Bedi</t>
+          <t>Meher Gupta</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Hargun Thind</t>
+          <t>Sahil Saini</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Sukhmani Goyal</t>
+          <t>Aditi Verma</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Ishaan Malhi</t>
+          <t>Ekamjot Kapoor</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -8842,7 +8842,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Nikita Gill</t>
+          <t>Avneet Pannu</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -8869,7 +8869,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Simran Kaur</t>
+          <t>Manjot Dhillon</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Karan Mehta</t>
+          <t>Arjun Rana</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -8923,7 +8923,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Mehakpreet Dhillon</t>
+          <t>Manav Mehta</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Gurnoor Kapoor</t>
+          <t>Riya Aulakh</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Rajbir Saini</t>
+          <t>Zoya Kaur</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Harleen Jain</t>
+          <t>Arshdeep Chawla</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Navjot Bhatia</t>
+          <t>Yuvraj Gill</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Sanya Sharma</t>
+          <t>Lovepreet Sidhu</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -9085,7 +9085,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Gurleen Singh</t>
+          <t>Ananya Malhi</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Jashan Arora</t>
+          <t>Kavya Sandhu</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Fatehbir Sandhu</t>
+          <t>Rahul Goyal</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Prabhleen Sidhu</t>
+          <t>Vansh Arora</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -9193,7 +9193,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Diya Chawla</t>
+          <t>Sneha Thind</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Meher Aulakh</t>
+          <t>Taranpreet Singh</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Sahil Rana</t>
+          <t>Khushi Bedi</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -9274,7 +9274,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Aditi Pannu</t>
+          <t>Aarav Gill</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Ekamjot Verma</t>
+          <t>Kabir Sidhu</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Avneet Gupta</t>
+          <t>Priya Malhi</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Manjot Bansal</t>
+          <t>Uday Sandhu</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Arjun Grewal</t>
+          <t>Rohan Goyal</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -9409,7 +9409,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Manav Bedi</t>
+          <t>Sehaj Arora</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Riya Thind</t>
+          <t>Japneet Thind</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Zoya Goyal</t>
+          <t>Vihaan Singh</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -9490,7 +9490,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Arshdeep Malhi</t>
+          <t>Jasleen Bedi</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Yuvraj Gill</t>
+          <t>Pranav Sharma</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Lovepreet Kaur</t>
+          <t>Tanvi Grewal</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Ananya Mehta</t>
+          <t>Muskan Bhatia</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Kavya Dhillon</t>
+          <t>Noor Bansal</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -9625,7 +9625,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Rahul Kapoor</t>
+          <t>Hargun Jain</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -9652,7 +9652,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Vansh Saini</t>
+          <t>Sukhmani Gupta</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Sneha Jain</t>
+          <t>Ishaan Saini</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -9706,7 +9706,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Taranpreet Bhatia</t>
+          <t>Nikita Verma</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Khushi Sharma</t>
+          <t>Simran Kapoor</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Aarav Singh</t>
+          <t>Karan Pannu</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Kabir Arora</t>
+          <t>Mehakpreet Dhillon</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Priya Sandhu</t>
+          <t>Gurnoor Rana</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Uday Sidhu</t>
+          <t>Rajbir Mehta</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Rohan Chawla</t>
+          <t>Harleen Aulakh</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -9895,7 +9895,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Sehaj Aulakh</t>
+          <t>Navjot Kaur</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Japneet Rana</t>
+          <t>Sanya Chawla</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Vihaan Pannu</t>
+          <t>Karan Verma</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -9976,7 +9976,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Jasleen Verma</t>
+          <t>Mehakpreet Kapoor</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Pranav Gupta</t>
+          <t>Gurnoor Pannu</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Tanvi Bansal</t>
+          <t>Rajbir Dhillon</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -10057,7 +10057,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Kabir Mehta</t>
+          <t>Harleen Rana</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Priya Dhillon</t>
+          <t>Navjot Mehta</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Uday Kapoor</t>
+          <t>Sanya Aulakh</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Rohan Saini</t>
+          <t>Gurleen Kaur</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Sehaj Jain</t>
+          <t>Jashan Chawla</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Japneet Bhatia</t>
+          <t>Fatehbir Gill</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -10219,7 +10219,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Vihaan Sharma</t>
+          <t>Prabhleen Sidhu</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Jasleen Singh</t>
+          <t>Diya Malhi</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Pranav Arora</t>
+          <t>Meher Sandhu</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -10300,7 +10300,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Tanvi Sandhu</t>
+          <t>Sahil Goyal</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Muskan Sidhu</t>
+          <t>Aditi Arora</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Noor Chawla</t>
+          <t>Ekamjot Thind</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Hargun Aulakh</t>
+          <t>Avneet Singh</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Sukhmani Rana</t>
+          <t>Manjot Bedi</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Ishaan Pannu</t>
+          <t>Arjun Sharma</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Nikita Verma</t>
+          <t>Manav Grewal</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Simran Gupta</t>
+          <t>Riya Bhatia</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Karan Bansal</t>
+          <t>Zoya Bansal</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -10543,7 +10543,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Mehakpreet Grewal</t>
+          <t>Arshdeep Jain</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Gurnoor Bedi</t>
+          <t>Yuvraj Gupta</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -10597,7 +10597,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Rajbir Thind</t>
+          <t>Lovepreet Saini</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -10624,7 +10624,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Harleen Goyal</t>
+          <t>Ananya Singh</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Navjot Malhi</t>
+          <t>Kavya Bedi</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Sanya Gill</t>
+          <t>Rahul Sharma</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -10705,7 +10705,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Gurleen Kaur</t>
+          <t>Vansh Grewal</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -10732,7 +10732,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Jashan Mehta</t>
+          <t>Sneha Bhatia</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -10759,7 +10759,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Fatehbir Dhillon</t>
+          <t>Taranpreet Bansal</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Prabhleen Kapoor</t>
+          <t>Khushi Jain</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Diya Saini</t>
+          <t>Aarav Gupta</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Meher Jain</t>
+          <t>Kabir Saini</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Sahil Bhatia</t>
+          <t>Priya Verma</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Aditi Sharma</t>
+          <t>Uday Kapoor</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Ekamjot Singh</t>
+          <t>Rohan Pannu</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -10948,7 +10948,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Avneet Arora</t>
+          <t>Sehaj Dhillon</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Manjot Sandhu</t>
+          <t>Japneet Rana</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Arjun Sidhu</t>
+          <t>Vihaan Mehta</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Manav Chawla</t>
+          <t>Jasleen Aulakh</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Riya Aulakh</t>
+          <t>Pranav Kaur</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Zoya Rana</t>
+          <t>Tanvi Chawla</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Arshdeep Pannu</t>
+          <t>Muskan Gill</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -11137,7 +11137,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Yuvraj Verma</t>
+          <t>Noor Sidhu</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -11164,7 +11164,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Lovepreet Gupta</t>
+          <t>Hargun Malhi</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Ananya Bansal</t>
+          <t>Sukhmani Sandhu</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Kavya Grewal</t>
+          <t>Ishaan Goyal</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Rahul Bedi</t>
+          <t>Nikita Arora</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Vansh Thind</t>
+          <t>Simran Thind</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Sneha Goyal</t>
+          <t>Muskan Kaur</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Taranpreet Malhi</t>
+          <t>Noor Chawla</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -11353,7 +11353,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Khushi Gill</t>
+          <t>Hargun Gill</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -11380,7 +11380,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Aarav Kaur</t>
+          <t>Sukhmani Sidhu</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Kabir Mehta</t>
+          <t>Ishaan Malhi</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Priya Dhillon</t>
+          <t>Nikita Sandhu</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -11461,7 +11461,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Uday Kapoor</t>
+          <t>Simran Goyal</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -11488,7 +11488,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Rohan Saini</t>
+          <t>Karan Arora</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -11515,7 +11515,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Sehaj Jain</t>
+          <t>Mehakpreet Thind</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -11542,7 +11542,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Japneet Bhatia</t>
+          <t>Gurnoor Singh</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -11569,7 +11569,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Vihaan Sharma</t>
+          <t>Rajbir Bedi</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -11596,7 +11596,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Jasleen Singh</t>
+          <t>Harleen Sharma</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -11623,7 +11623,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Pranav Arora</t>
+          <t>Navjot Grewal</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Tanvi Sandhu</t>
+          <t>Sanya Bhatia</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">

--- a/docs/demo-data/GNDEC/GNDEC_4_ME.xlsx
+++ b/docs/demo-data/GNDEC/GNDEC_4_ME.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -472,178 +472,185 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>then CSE, IT, ME and CE. Shared halls, the JPAL hour and the final-year CSE elective are set up by</t>
+          <t>then CSE, IT, ME and CE. Its file also has the lecture theatres, drawing halls and workshops of</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>the College Admin (they are already in the built-in GNDEC demo college).</t>
+          <t>first year. Not in the files: the JPAL hour and the final-year CSE elective (they need a student list</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>per group; they are in the built-in GNDEC demo college).</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Timetabl.ai: one department's data</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-    </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Fill one file per department and upload it on the department's page (Setup &gt; Departments &gt; Upload Excel).</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Fill one file per department and upload it on the department's page (Setup &gt; Departments &gt; Upload Excel).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Rows are checked before anything is saved; problems are shown row by row. A '*' marks a required column.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Sections: one row per section (a group of students who always sit together).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Section: its name, e.g. D2CS-A. Year: 1-4. Students: how many. Shift: the shift name from Setup (e.g. Day).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Section: its name, e.g. D2CS-A. Year: 1-4. Students: how many. Shift: the shift name from Setup (e.g. Day).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Lab batches: how the section splits for labs, e.g. 'A1:30, A2:30' (name:students). Empty = whole section.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Teachers: one row per teacher of the department.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t xml:space="preserve">  Name, Email (their login), Shifts (one or more shift names, comma separated), Max periods per day (default 5).</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Subjects: one row per subject the department teaches.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Code, Name, Year, Lectures per week, Labs per week (lab blocks; one block = the college's lab length, e.g. 2 periods),</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Code, Name, Year, Lectures per week, Labs per week (lab blocks; one block = the college's lab length, e.g. 2 periods),</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Lab equipment: what the lab room must have, e.g. computers. It must match a lab room's Equipment.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Can teach: which subjects each teacher can teach. Preference 1 = first choice, 2 = could also teach it.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t xml:space="preserve">  Used for teacher suggestions and to find a substitute when a teacher is on leave.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Classes: one row per class. Subject code, Sections (several separated by commas = one combined class),</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Type (Lecture or Lab), Batch ('all' = one lab for each lab batch, or one batch name), Teacher (may be empty).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  A teacher or subject of another department (e.g. Applied Sciences for first-year maths) can be named too,</t>
+          <t xml:space="preserve">  Type (Lecture or Lab), Batch ('all' = one lab for each lab batch, or one batch name), Teacher (may be empty).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t xml:space="preserve">  A teacher or subject of another department (e.g. Applied Sciences for first-year maths) can be named too,</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t xml:space="preserve">  once that department's file is uploaded: upload Applied Sciences first.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Students: Roll no, Name, Email (their login; first password = roll number), Section, Batch.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
+          <t>Students: Roll no, Name, Email (their login; first password = roll number), Section, Batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
           <t>Rooms: rooms this department owns. Type: Lecture, Lab or Seminar. Seats. Equipment for labs.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Shared halls (lecture theatres, seminar hall, drawing halls, workshops) are added by the College Admin in Setup.</t>
-        </is>
-      </c>
-    </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Rooms every department may use (e.g. a seminar hall) are added by the College Admin in Setup as shared rooms.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Not in this file: the time grid, lunch window, holidays, electives and pooled groups (e.g. JPAL),</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
+        <is>
+          <t>Not in this file: the time grid, lunch window, holidays, electives and pooled groups (e.g. JPAL),</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>rules and shared rooms. The College Admin sets those in Setup.</t>
         </is>

--- a/docs/demo-data/GNDEC/GNDEC_4_ME.xlsx
+++ b/docs/demo-data/GNDEC/GNDEC_4_ME.xlsx
@@ -3643,7 +3643,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2613001@gndec.demo</t>
+          <t>2613001@gndec.test</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2613002@gndec.demo</t>
+          <t>2613002@gndec.test</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2613003@gndec.demo</t>
+          <t>2613003@gndec.test</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2613004@gndec.demo</t>
+          <t>2613004@gndec.test</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2613005@gndec.demo</t>
+          <t>2613005@gndec.test</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2613006@gndec.demo</t>
+          <t>2613006@gndec.test</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2613007@gndec.demo</t>
+          <t>2613007@gndec.test</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2613008@gndec.demo</t>
+          <t>2613008@gndec.test</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2613009@gndec.demo</t>
+          <t>2613009@gndec.test</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2613010@gndec.demo</t>
+          <t>2613010@gndec.test</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2613011@gndec.demo</t>
+          <t>2613011@gndec.test</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2613012@gndec.demo</t>
+          <t>2613012@gndec.test</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2613013@gndec.demo</t>
+          <t>2613013@gndec.test</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2613014@gndec.demo</t>
+          <t>2613014@gndec.test</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2613015@gndec.demo</t>
+          <t>2613015@gndec.test</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2613016@gndec.demo</t>
+          <t>2613016@gndec.test</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2613017@gndec.demo</t>
+          <t>2613017@gndec.test</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2613018@gndec.demo</t>
+          <t>2613018@gndec.test</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2613019@gndec.demo</t>
+          <t>2613019@gndec.test</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2613020@gndec.demo</t>
+          <t>2613020@gndec.test</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2613021@gndec.demo</t>
+          <t>2613021@gndec.test</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2613022@gndec.demo</t>
+          <t>2613022@gndec.test</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2613023@gndec.demo</t>
+          <t>2613023@gndec.test</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2613024@gndec.demo</t>
+          <t>2613024@gndec.test</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2613025@gndec.demo</t>
+          <t>2613025@gndec.test</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2613026@gndec.demo</t>
+          <t>2613026@gndec.test</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2613027@gndec.demo</t>
+          <t>2613027@gndec.test</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2613028@gndec.demo</t>
+          <t>2613028@gndec.test</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2613029@gndec.demo</t>
+          <t>2613029@gndec.test</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2613030@gndec.demo</t>
+          <t>2613030@gndec.test</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2613031@gndec.demo</t>
+          <t>2613031@gndec.test</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2613032@gndec.demo</t>
+          <t>2613032@gndec.test</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2613033@gndec.demo</t>
+          <t>2613033@gndec.test</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2613034@gndec.demo</t>
+          <t>2613034@gndec.test</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2613035@gndec.demo</t>
+          <t>2613035@gndec.test</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2613036@gndec.demo</t>
+          <t>2613036@gndec.test</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2613037@gndec.demo</t>
+          <t>2613037@gndec.test</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2613038@gndec.demo</t>
+          <t>2613038@gndec.test</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2613039@gndec.demo</t>
+          <t>2613039@gndec.test</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2613040@gndec.demo</t>
+          <t>2613040@gndec.test</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2613041@gndec.demo</t>
+          <t>2613041@gndec.test</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2613042@gndec.demo</t>
+          <t>2613042@gndec.test</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2613043@gndec.demo</t>
+          <t>2613043@gndec.test</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2613044@gndec.demo</t>
+          <t>2613044@gndec.test</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2613045@gndec.demo</t>
+          <t>2613045@gndec.test</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2613046@gndec.demo</t>
+          <t>2613046@gndec.test</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2613047@gndec.demo</t>
+          <t>2613047@gndec.test</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2613048@gndec.demo</t>
+          <t>2613048@gndec.test</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2613049@gndec.demo</t>
+          <t>2613049@gndec.test</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2613050@gndec.demo</t>
+          <t>2613050@gndec.test</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2613051@gndec.demo</t>
+          <t>2613051@gndec.test</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2613052@gndec.demo</t>
+          <t>2613052@gndec.test</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2613053@gndec.demo</t>
+          <t>2613053@gndec.test</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2613054@gndec.demo</t>
+          <t>2613054@gndec.test</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2613055@gndec.demo</t>
+          <t>2613055@gndec.test</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2613056@gndec.demo</t>
+          <t>2613056@gndec.test</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2613057@gndec.demo</t>
+          <t>2613057@gndec.test</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2613058@gndec.demo</t>
+          <t>2613058@gndec.test</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2613059@gndec.demo</t>
+          <t>2613059@gndec.test</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2613060@gndec.demo</t>
+          <t>2613060@gndec.test</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2513001@gndec.demo</t>
+          <t>2513001@gndec.test</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2513002@gndec.demo</t>
+          <t>2513002@gndec.test</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2513003@gndec.demo</t>
+          <t>2513003@gndec.test</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2513004@gndec.demo</t>
+          <t>2513004@gndec.test</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2513005@gndec.demo</t>
+          <t>2513005@gndec.test</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2513006@gndec.demo</t>
+          <t>2513006@gndec.test</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2513007@gndec.demo</t>
+          <t>2513007@gndec.test</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2513008@gndec.demo</t>
+          <t>2513008@gndec.test</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2513009@gndec.demo</t>
+          <t>2513009@gndec.test</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2513010@gndec.demo</t>
+          <t>2513010@gndec.test</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2513011@gndec.demo</t>
+          <t>2513011@gndec.test</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2513012@gndec.demo</t>
+          <t>2513012@gndec.test</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2513013@gndec.demo</t>
+          <t>2513013@gndec.test</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2513014@gndec.demo</t>
+          <t>2513014@gndec.test</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2513015@gndec.demo</t>
+          <t>2513015@gndec.test</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2513016@gndec.demo</t>
+          <t>2513016@gndec.test</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2513017@gndec.demo</t>
+          <t>2513017@gndec.test</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2513018@gndec.demo</t>
+          <t>2513018@gndec.test</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2513019@gndec.demo</t>
+          <t>2513019@gndec.test</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2513020@gndec.demo</t>
+          <t>2513020@gndec.test</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2513021@gndec.demo</t>
+          <t>2513021@gndec.test</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2513022@gndec.demo</t>
+          <t>2513022@gndec.test</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2513023@gndec.demo</t>
+          <t>2513023@gndec.test</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2513024@gndec.demo</t>
+          <t>2513024@gndec.test</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2513025@gndec.demo</t>
+          <t>2513025@gndec.test</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2513026@gndec.demo</t>
+          <t>2513026@gndec.test</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2513027@gndec.demo</t>
+          <t>2513027@gndec.test</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2513028@gndec.demo</t>
+          <t>2513028@gndec.test</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2513029@gndec.demo</t>
+          <t>2513029@gndec.test</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2513030@gndec.demo</t>
+          <t>2513030@gndec.test</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2513031@gndec.demo</t>
+          <t>2513031@gndec.test</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2513032@gndec.demo</t>
+          <t>2513032@gndec.test</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2513033@gndec.demo</t>
+          <t>2513033@gndec.test</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2513034@gndec.demo</t>
+          <t>2513034@gndec.test</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2513035@gndec.demo</t>
+          <t>2513035@gndec.test</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2513036@gndec.demo</t>
+          <t>2513036@gndec.test</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2513037@gndec.demo</t>
+          <t>2513037@gndec.test</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2513038@gndec.demo</t>
+          <t>2513038@gndec.test</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2513039@gndec.demo</t>
+          <t>2513039@gndec.test</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2513040@gndec.demo</t>
+          <t>2513040@gndec.test</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2513041@gndec.demo</t>
+          <t>2513041@gndec.test</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2513042@gndec.demo</t>
+          <t>2513042@gndec.test</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2513043@gndec.demo</t>
+          <t>2513043@gndec.test</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2513044@gndec.demo</t>
+          <t>2513044@gndec.test</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2513045@gndec.demo</t>
+          <t>2513045@gndec.test</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2513046@gndec.demo</t>
+          <t>2513046@gndec.test</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2513047@gndec.demo</t>
+          <t>2513047@gndec.test</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2513048@gndec.demo</t>
+          <t>2513048@gndec.test</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2513049@gndec.demo</t>
+          <t>2513049@gndec.test</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2513050@gndec.demo</t>
+          <t>2513050@gndec.test</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2513051@gndec.demo</t>
+          <t>2513051@gndec.test</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2513052@gndec.demo</t>
+          <t>2513052@gndec.test</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2513053@gndec.demo</t>
+          <t>2513053@gndec.test</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2513054@gndec.demo</t>
+          <t>2513054@gndec.test</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2513055@gndec.demo</t>
+          <t>2513055@gndec.test</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2513056@gndec.demo</t>
+          <t>2513056@gndec.test</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2513057@gndec.demo</t>
+          <t>2513057@gndec.test</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2513058@gndec.demo</t>
+          <t>2513058@gndec.test</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2513059@gndec.demo</t>
+          <t>2513059@gndec.test</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2513060@gndec.demo</t>
+          <t>2513060@gndec.test</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2513061@gndec.demo</t>
+          <t>2513061@gndec.test</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2513062@gndec.demo</t>
+          <t>2513062@gndec.test</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2513063@gndec.demo</t>
+          <t>2513063@gndec.test</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2513064@gndec.demo</t>
+          <t>2513064@gndec.test</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2513065@gndec.demo</t>
+          <t>2513065@gndec.test</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2513066@gndec.demo</t>
+          <t>2513066@gndec.test</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2513067@gndec.demo</t>
+          <t>2513067@gndec.test</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2513068@gndec.demo</t>
+          <t>2513068@gndec.test</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2513069@gndec.demo</t>
+          <t>2513069@gndec.test</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2513070@gndec.demo</t>
+          <t>2513070@gndec.test</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2513071@gndec.demo</t>
+          <t>2513071@gndec.test</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2513072@gndec.demo</t>
+          <t>2513072@gndec.test</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2513073@gndec.demo</t>
+          <t>2513073@gndec.test</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2513074@gndec.demo</t>
+          <t>2513074@gndec.test</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2513075@gndec.demo</t>
+          <t>2513075@gndec.test</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2513076@gndec.demo</t>
+          <t>2513076@gndec.test</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2513077@gndec.demo</t>
+          <t>2513077@gndec.test</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7342,7 +7342,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2513078@gndec.demo</t>
+          <t>2513078@gndec.test</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2513079@gndec.demo</t>
+          <t>2513079@gndec.test</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2513080@gndec.demo</t>
+          <t>2513080@gndec.test</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2513081@gndec.demo</t>
+          <t>2513081@gndec.test</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2513082@gndec.demo</t>
+          <t>2513082@gndec.test</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2513083@gndec.demo</t>
+          <t>2513083@gndec.test</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2513084@gndec.demo</t>
+          <t>2513084@gndec.test</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2513085@gndec.demo</t>
+          <t>2513085@gndec.test</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2513086@gndec.demo</t>
+          <t>2513086@gndec.test</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2513087@gndec.demo</t>
+          <t>2513087@gndec.test</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2513088@gndec.demo</t>
+          <t>2513088@gndec.test</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2513089@gndec.demo</t>
+          <t>2513089@gndec.test</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2513090@gndec.demo</t>
+          <t>2513090@gndec.test</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2513091@gndec.demo</t>
+          <t>2513091@gndec.test</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2513092@gndec.demo</t>
+          <t>2513092@gndec.test</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2513093@gndec.demo</t>
+          <t>2513093@gndec.test</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2513094@gndec.demo</t>
+          <t>2513094@gndec.test</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2513095@gndec.demo</t>
+          <t>2513095@gndec.test</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2513096@gndec.demo</t>
+          <t>2513096@gndec.test</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2513097@gndec.demo</t>
+          <t>2513097@gndec.test</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2513098@gndec.demo</t>
+          <t>2513098@gndec.test</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2513099@gndec.demo</t>
+          <t>2513099@gndec.test</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2513100@gndec.demo</t>
+          <t>2513100@gndec.test</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2513101@gndec.demo</t>
+          <t>2513101@gndec.test</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2513102@gndec.demo</t>
+          <t>2513102@gndec.test</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2513103@gndec.demo</t>
+          <t>2513103@gndec.test</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -8044,7 +8044,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2513104@gndec.demo</t>
+          <t>2513104@gndec.test</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2513105@gndec.demo</t>
+          <t>2513105@gndec.test</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2513106@gndec.demo</t>
+          <t>2513106@gndec.test</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2513107@gndec.demo</t>
+          <t>2513107@gndec.test</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2513108@gndec.demo</t>
+          <t>2513108@gndec.test</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2513109@gndec.demo</t>
+          <t>2513109@gndec.test</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -8206,7 +8206,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2513110@gndec.demo</t>
+          <t>2513110@gndec.test</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2513111@gndec.demo</t>
+          <t>2513111@gndec.test</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2513112@gndec.demo</t>
+          <t>2513112@gndec.test</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2513113@gndec.demo</t>
+          <t>2513113@gndec.test</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2513114@gndec.demo</t>
+          <t>2513114@gndec.test</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2513115@gndec.demo</t>
+          <t>2513115@gndec.test</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2513116@gndec.demo</t>
+          <t>2513116@gndec.test</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2513117@gndec.demo</t>
+          <t>2513117@gndec.test</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2513118@gndec.demo</t>
+          <t>2513118@gndec.test</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2413001@gndec.demo</t>
+          <t>2413001@gndec.test</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2413002@gndec.demo</t>
+          <t>2413002@gndec.test</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2413003@gndec.demo</t>
+          <t>2413003@gndec.test</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2413004@gndec.demo</t>
+          <t>2413004@gndec.test</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2413005@gndec.demo</t>
+          <t>2413005@gndec.test</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2413006@gndec.demo</t>
+          <t>2413006@gndec.test</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2413007@gndec.demo</t>
+          <t>2413007@gndec.test</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2413008@gndec.demo</t>
+          <t>2413008@gndec.test</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2413009@gndec.demo</t>
+          <t>2413009@gndec.test</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -8692,7 +8692,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2413010@gndec.demo</t>
+          <t>2413010@gndec.test</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2413011@gndec.demo</t>
+          <t>2413011@gndec.test</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2413012@gndec.demo</t>
+          <t>2413012@gndec.test</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2413013@gndec.demo</t>
+          <t>2413013@gndec.test</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -8800,7 +8800,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2413014@gndec.demo</t>
+          <t>2413014@gndec.test</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2413015@gndec.demo</t>
+          <t>2413015@gndec.test</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2413016@gndec.demo</t>
+          <t>2413016@gndec.test</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2413017@gndec.demo</t>
+          <t>2413017@gndec.test</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2413018@gndec.demo</t>
+          <t>2413018@gndec.test</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2413019@gndec.demo</t>
+          <t>2413019@gndec.test</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2413020@gndec.demo</t>
+          <t>2413020@gndec.test</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2413021@gndec.demo</t>
+          <t>2413021@gndec.test</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -9016,7 +9016,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2413022@gndec.demo</t>
+          <t>2413022@gndec.test</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2413023@gndec.demo</t>
+          <t>2413023@gndec.test</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2413024@gndec.demo</t>
+          <t>2413024@gndec.test</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2413025@gndec.demo</t>
+          <t>2413025@gndec.test</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2413026@gndec.demo</t>
+          <t>2413026@gndec.test</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2413027@gndec.demo</t>
+          <t>2413027@gndec.test</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2413028@gndec.demo</t>
+          <t>2413028@gndec.test</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2413029@gndec.demo</t>
+          <t>2413029@gndec.test</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2413030@gndec.demo</t>
+          <t>2413030@gndec.test</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2413031@gndec.demo</t>
+          <t>2413031@gndec.test</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2413032@gndec.demo</t>
+          <t>2413032@gndec.test</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2413033@gndec.demo</t>
+          <t>2413033@gndec.test</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2413034@gndec.demo</t>
+          <t>2413034@gndec.test</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2413035@gndec.demo</t>
+          <t>2413035@gndec.test</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2413036@gndec.demo</t>
+          <t>2413036@gndec.test</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2413037@gndec.demo</t>
+          <t>2413037@gndec.test</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2413038@gndec.demo</t>
+          <t>2413038@gndec.test</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2413039@gndec.demo</t>
+          <t>2413039@gndec.test</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2413040@gndec.demo</t>
+          <t>2413040@gndec.test</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2413041@gndec.demo</t>
+          <t>2413041@gndec.test</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2413042@gndec.demo</t>
+          <t>2413042@gndec.test</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2413043@gndec.demo</t>
+          <t>2413043@gndec.test</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2413044@gndec.demo</t>
+          <t>2413044@gndec.test</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2413045@gndec.demo</t>
+          <t>2413045@gndec.test</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2413046@gndec.demo</t>
+          <t>2413046@gndec.test</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2413047@gndec.demo</t>
+          <t>2413047@gndec.test</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2413048@gndec.demo</t>
+          <t>2413048@gndec.test</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -9745,7 +9745,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2413049@gndec.demo</t>
+          <t>2413049@gndec.test</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -9772,7 +9772,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2413050@gndec.demo</t>
+          <t>2413050@gndec.test</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2413051@gndec.demo</t>
+          <t>2413051@gndec.test</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2413052@gndec.demo</t>
+          <t>2413052@gndec.test</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2413053@gndec.demo</t>
+          <t>2413053@gndec.test</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2413054@gndec.demo</t>
+          <t>2413054@gndec.test</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2413055@gndec.demo</t>
+          <t>2413055@gndec.test</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -9934,7 +9934,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2413056@gndec.demo</t>
+          <t>2413056@gndec.test</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2413057@gndec.demo</t>
+          <t>2413057@gndec.test</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2413058@gndec.demo</t>
+          <t>2413058@gndec.test</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2413059@gndec.demo</t>
+          <t>2413059@gndec.test</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2413060@gndec.demo</t>
+          <t>2413060@gndec.test</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2313001@gndec.demo</t>
+          <t>2313001@gndec.test</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2313002@gndec.demo</t>
+          <t>2313002@gndec.test</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2313003@gndec.demo</t>
+          <t>2313003@gndec.test</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2313004@gndec.demo</t>
+          <t>2313004@gndec.test</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2313005@gndec.demo</t>
+          <t>2313005@gndec.test</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -10204,7 +10204,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2313006@gndec.demo</t>
+          <t>2313006@gndec.test</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2313007@gndec.demo</t>
+          <t>2313007@gndec.test</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2313008@gndec.demo</t>
+          <t>2313008@gndec.test</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2313009@gndec.demo</t>
+          <t>2313009@gndec.test</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2313010@gndec.demo</t>
+          <t>2313010@gndec.test</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2313011@gndec.demo</t>
+          <t>2313011@gndec.test</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2313012@gndec.demo</t>
+          <t>2313012@gndec.test</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2313013@gndec.demo</t>
+          <t>2313013@gndec.test</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2313014@gndec.demo</t>
+          <t>2313014@gndec.test</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2313015@gndec.demo</t>
+          <t>2313015@gndec.test</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -10474,7 +10474,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2313016@gndec.demo</t>
+          <t>2313016@gndec.test</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2313017@gndec.demo</t>
+          <t>2313017@gndec.test</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>2313018@gndec.demo</t>
+          <t>2313018@gndec.test</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>2313019@gndec.demo</t>
+          <t>2313019@gndec.test</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>2313020@gndec.demo</t>
+          <t>2313020@gndec.test</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>2313021@gndec.demo</t>
+          <t>2313021@gndec.test</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -10636,7 +10636,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>2313022@gndec.demo</t>
+          <t>2313022@gndec.test</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -10663,7 +10663,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>2313023@gndec.demo</t>
+          <t>2313023@gndec.test</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>2313024@gndec.demo</t>
+          <t>2313024@gndec.test</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>2313025@gndec.demo</t>
+          <t>2313025@gndec.test</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2313026@gndec.demo</t>
+          <t>2313026@gndec.test</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2313027@gndec.demo</t>
+          <t>2313027@gndec.test</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2313028@gndec.demo</t>
+          <t>2313028@gndec.test</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2313029@gndec.demo</t>
+          <t>2313029@gndec.test</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -10852,7 +10852,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2313030@gndec.demo</t>
+          <t>2313030@gndec.test</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -10879,7 +10879,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2313031@gndec.demo</t>
+          <t>2313031@gndec.test</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -10906,7 +10906,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2313032@gndec.demo</t>
+          <t>2313032@gndec.test</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -10933,7 +10933,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2313033@gndec.demo</t>
+          <t>2313033@gndec.test</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2313034@gndec.demo</t>
+          <t>2313034@gndec.test</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -10987,7 +10987,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2313035@gndec.demo</t>
+          <t>2313035@gndec.test</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2313036@gndec.demo</t>
+          <t>2313036@gndec.test</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2313037@gndec.demo</t>
+          <t>2313037@gndec.test</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2313038@gndec.demo</t>
+          <t>2313038@gndec.test</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2313039@gndec.demo</t>
+          <t>2313039@gndec.test</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>2313040@gndec.demo</t>
+          <t>2313040@gndec.test</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -11149,7 +11149,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>2313041@gndec.demo</t>
+          <t>2313041@gndec.test</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2313042@gndec.demo</t>
+          <t>2313042@gndec.test</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -11203,7 +11203,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2313043@gndec.demo</t>
+          <t>2313043@gndec.test</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>2313044@gndec.demo</t>
+          <t>2313044@gndec.test</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2313045@gndec.demo</t>
+          <t>2313045@gndec.test</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2313046@gndec.demo</t>
+          <t>2313046@gndec.test</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>2313047@gndec.demo</t>
+          <t>2313047@gndec.test</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -11338,7 +11338,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>2313048@gndec.demo</t>
+          <t>2313048@gndec.test</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -11365,7 +11365,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2313049@gndec.demo</t>
+          <t>2313049@gndec.test</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>2313050@gndec.demo</t>
+          <t>2313050@gndec.test</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2313051@gndec.demo</t>
+          <t>2313051@gndec.test</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2313052@gndec.demo</t>
+          <t>2313052@gndec.test</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2313053@gndec.demo</t>
+          <t>2313053@gndec.test</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>2313054@gndec.demo</t>
+          <t>2313054@gndec.test</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -11527,7 +11527,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>2313055@gndec.demo</t>
+          <t>2313055@gndec.test</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -11554,7 +11554,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>2313056@gndec.demo</t>
+          <t>2313056@gndec.test</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -11581,7 +11581,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>2313057@gndec.demo</t>
+          <t>2313057@gndec.test</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -11608,7 +11608,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2313058@gndec.demo</t>
+          <t>2313058@gndec.test</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2313059@gndec.demo</t>
+          <t>2313059@gndec.test</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -11662,7 +11662,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2313060@gndec.demo</t>
+          <t>2313060@gndec.test</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
